--- a/meta/16-1-1.xlsx
+++ b/meta/16-1-1.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7FC0245-34E8-41E6-BF32-8C3CE9036B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист" sheetId="2" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
@@ -100,78 +101,67 @@
     <t>16.1: Значительно сократить распространенность всех форм насилия и уменьшить показатели смертности от этого явления во всем мире</t>
   </si>
   <si>
-    <t>Национальный статистический комитет КР (Отдел демографической статистики)</t>
-  </si>
-  <si>
-    <t>Таипова Т.С.</t>
-  </si>
-  <si>
-    <t>t.taipova@stat.kg, tamarataipova@mail.ru</t>
-  </si>
-  <si>
-    <t>(312) 32 46 36</t>
-  </si>
-  <si>
-    <t>Общее число жертв умышленных убийств, деленное на общее количество населения, в расчете на 100 000 человек</t>
+    <t xml:space="preserve">16.1.1 Число жертв умышленных убийств на 100 000 человек в разбивке по полу и возрасту </t>
+  </si>
+  <si>
+    <t>Генеральная прокуратура Кыргызской Республики</t>
+  </si>
+  <si>
+    <t>Кармышалиева А.А.</t>
+  </si>
+  <si>
+    <t>aselkarmyshalieva2022@gmail.com</t>
+  </si>
+  <si>
+    <t>(312) 56-70-19 доп.2005</t>
+  </si>
+  <si>
+    <t>www.prokuror.kg</t>
+  </si>
+  <si>
+    <t>Общее число жертв умышленных убийств, деленное на численность населения, в расчете на 100 000 человек.</t>
   </si>
   <si>
     <t>Умышленным убийством признается незаконная смерть, причиненная человеку с намерением вызвать смерть или нанести серьезные увечья. (Источник: Международная классификация Преступлений для целей Статистики, ICCS 2015).</t>
   </si>
   <si>
-    <t xml:space="preserve"> Данный показатель широко используется на национальном и международном уровнях для оценки самых крайних форм жестоких преступлений, а также показывает явные слабые стороны системы безопасности граждан. Обеспечение безопасности от насилия является необходимым условием для людей, чтобы жить безопасной и активной жизнью, она также необходима для свободного развития общества и экономики. Умышленные убийства происходят во всех странах мира, этот показатель имеет глобальный масштаб.
-Необходимо проводить мониторинг умышленных убийств, чтобы лучше понимать их причины, помыслы и последствия и, в долгосрочной перспективе, разрабатывать эффективные профилактические мероприятия. Если данные верно детализированы (согласно Международной классификации Преступлений для целей Статистики, ICCS 2015), то показатель может определить различные виды насилия, связанного с убийством: межличностные (включая насилие партнера семейное насилие), преступные (в том числе организованная преступность и другие формы преступной деятельности), социально-политические (в том числе терроризм и преступления на почве ненависти).</t>
-  </si>
-  <si>
-    <t>Источником информации о причинах смерти являются записи в медицинских свидетельствах о смерти, составляемых врачом или средним медицинским персоналом относительно заболевания, несчастного случая, убийства, самоубийства и другого внешнего воздействия, послуживших причиной смерти. Эти документы вместе с актовыми записями о смерти направляются для разработки в органы государственной статистики.</t>
-  </si>
-  <si>
-    <t>Сведения о смертях получаются на основании ежегодной статистической разработки данных, содержащихся в актовых записях о смерти, составляемых органами записи актов гражданского состояния.  Агрегированные данные собираются и обрабатываются областными управлениями статистики и НСК КР.</t>
+    <t>Индикатор используется для оценки уровня самых крайних форм насилия и состояния общественной безопасности. Мониторинг умышленных убийств необходим для понимания их причин и последствий, а также для разработки эффективных профилактических мер и государственных программ по снижению уровня насилия.</t>
+  </si>
+  <si>
+    <t>Единый реестр преступлений Генеральной прокуратуры Кыргызской Республики.</t>
+  </si>
+  <si>
+    <t>Административные данные правоохранительных органов, внесенных регистраторами в АИС "ЕРП"..</t>
   </si>
   <si>
     <t>Отношение числа умерших от умышленных убийств к среднегодовой численности постоянного населения по текущей оценке. Рассчитывается на 100 000 населения.</t>
   </si>
   <si>
-    <t>Международная классификация Преступлений для целей Статистики, ICCS 2015 приводит важные разъяснения определения умышленного убийства. В частности, утверждается, что нижеперечисленные виды преступлений также включаются в понятие умышленного убийства:
-- тяжкое убийство
-- убийство чести
-- серьезное нападение, ведущее к смерти
-- смерть в результате террористических действий
-- убийство, относящееся к выкупу
-- женоубийство (феминицид)
-- детоубийство
-- преднамеренное убийство
-- внесудебная казнь
-- убийство, связанное с превышением полномочий представителями закона.
-Кроме того, классификация дает определение, как отличить умышленные убийства, убийства, напрямую связанные с войной/конфликтами и другие убийства, которые равносильны военным преступлениям.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Проводится логический и арифметический контроль отчетных данных. Процедура проверки правильности данных в актовых записях о смерти осуществляется путем логического контроля, заложенного в программном обеспечении по вводу и разработке данных. Корректировка проставленных кодов причин смерти на соответствие диагнозам, записанным в актовой записи о смерти, согласно МКБ-10. Анализ выходных таблиц по причинам смерти.</t>
-  </si>
-  <si>
-    <t>Данные по смертности от самоубийств публикуются в статистических сборниках "Женщины и мужчины КР", «Социальные тенденции КР», "Статистический ежегодник КР", "Кыргызстан в цифрах", размещаются на сайте НСК.</t>
+    <t>В расчёт показателя включаются преступления, возбужденные по статье 122 Уголовного кодекса Кыргызской Республики, на стадии досудебного производства.</t>
+  </si>
+  <si>
+    <t>Проводится регулярная сверка данных с информацией, содержащейся в АИС «ЕРП», с целью обеспечения их полноты, точности и актуальности.</t>
+  </si>
+  <si>
+    <t>Данные доступны ежегодно начиная с 2015 года.</t>
   </si>
   <si>
     <t xml:space="preserve"> По территории - республика, область, район и по полу.</t>
   </si>
   <si>
-    <t>Национальное определение показателя, используемое в статистике, соответствует его международному определению. Кодирование и разработка данных об умерших по причинам смерти производятся органами государственной статистики на основании Международной статистической классификации болезней и причин смерти 10-го пересмотра (МКБ-10) Всемирной организации здравоохранения (ВОЗ), начиная с отчета за 2000г. По соглашению с НСК база данных по смертности передается Центру электронного здравоохранения КР при Министерстве здравоохранения: Форма 2 «Сведения о числе родившихся, браков, разводов и умерших по причинам смерти» – ежемесячно, с отставанием на 1,5 мес. от отчетного месяца и Форма С52 «Смертность населения по причинам смерти» – ежегодно, в июне месяце года, следующего за отчетным годом.</t>
-  </si>
-  <si>
-    <t>Национальная платформа отчетности ЦУР КР: https://sustainabledevelopment-kyrgyzstan.github.io 
-Ссылки на НПА и методологию: http://www.stat.kg/u/about/pravovye-osnovy-organov-gosudarstvennoj-statistiki/; https://unstats.un.org/sdgs/Metadata; http://www.stat.kg/ru/statistics/download/methodology/68/. Статистические публикации НСК: ежемесячный доклад «Социально-экономическое положение КР», статистические сборники: «Социальные тенденции КР», «Женщины и мужчины КР», «Здоровье населения и здравоохранение в КР» на официальном сайте НСК КР: http://www.stat.kg/ru/publications/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1.1 Число жертв умышленных убийств на 100 000 человек в разбивке по полу и возрасту </t>
-  </si>
-  <si>
-    <t>www.stat.gov.kg</t>
+    <t>Сравнимо с данными UNODC, IOM, но возможны расхождения из-за различий в национальной практике учета.</t>
+  </si>
+  <si>
+    <t>ICCS 2015
+www.prokuror.kg                                                                                                                                                                                                                                                                                                                                                            UNODC Global Study on Homicide
+ww w.stat.gov.kg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +199,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -249,11 +252,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -265,22 +272,50 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="6">
+    <cellStyle name="Гиперссылка 2" xfId="5" xr:uid="{44B2AF24-6335-4722-AE41-80C770B793F7}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="3" xr:uid="{CD193773-FCC0-4A9A-80BE-1092C9CDD5CA}"/>
+    <cellStyle name="Обычный 3" xfId="4" xr:uid="{2D87FF0E-49B1-4195-8E17-368E555E3FE8}"/>
+    <cellStyle name="Обычный 4" xfId="2" xr:uid="{8F004208-D29D-41D5-AE41-77FCC8EB6852}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -296,9 +331,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -336,9 +371,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -373,7 +408,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -408,7 +443,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -581,12 +616,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.85546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="71.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="99.140625" style="3" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -596,11 +631,11 @@
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -608,7 +643,7 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -616,8 +651,8 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>44</v>
+      <c r="B4" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -631,31 +666,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>29</v>
+      <c r="B7" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>30</v>
+      <c r="B8" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>31</v>
+      <c r="B9" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -663,7 +698,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -672,28 +707,28 @@
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="272.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>34</v>
+      <c r="B14" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -702,20 +737,20 @@
       </c>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>36</v>
+      <c r="B17" s="10" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -724,28 +759,28 @@
       </c>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="255.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>39</v>
+      <c r="B21" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -754,36 +789,36 @@
       </c>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>40</v>
+      <c r="B23" s="12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="183" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>43</v>
+      <c r="B26" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
